--- a/SGC-CKN/Excel/c1aec554-e595-4a95-adcb-8d158734d4d6_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-7_D800_13-03-2026.xlsx
+++ b/SGC-CKN/Excel/c1aec554-e595-4a95-adcb-8d158734d4d6_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-7_D800_13-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>17-7</t>
+    <t>P7-7</t>
   </si>
   <si>
     <t>Biên bản số</t>

--- a/SGC-CKN/Excel/c1aec554-e595-4a95-adcb-8d158734d4d6_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-7_D800_13-03-2026.xlsx
+++ b/SGC-CKN/Excel/c1aec554-e595-4a95-adcb-8d158734d4d6_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-7_D800_13-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="73">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P7-7</t>
+    <t>P7-07</t>
   </si>
   <si>
     <t>Biên bản số</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>3. Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">08:30
@@ -112,7 +112,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>5. Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">10:48
@@ -125,7 +125,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>9. Sét xám trắng, xám xanh dẻo chảy</t>
+    <t>Sét xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">11:33
@@ -138,7 +138,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>11. Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">13:05
@@ -151,7 +151,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>14. Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">14:00
@@ -164,7 +164,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>15. Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">14:30
@@ -177,7 +177,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>16. Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">15:40
@@ -190,7 +190,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1. Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xám, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">16:40
@@ -201,9 +201,6 @@
   </si>
   <si>
     <t>9</t>
-  </si>
-  <si>
-    <t>16. Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">20:23
@@ -1486,13 +1483,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>57</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F19" s="31">
         <v>0</v>
@@ -1510,12 +1507,12 @@
         <v>0.84</v>
       </c>
       <c r="K19" s="32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B22" s="35"/>
       <c r="C22" s="35"/>
@@ -1621,31 +1618,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1888,7 +1885,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1911,13 +1908,13 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="37" t="s">
-        <v>73</v>
-      </c>
       <c r="C11" s="37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D11" s="37">
         <v>9</v>
